--- a/orcamentos_abertos.xlsx
+++ b/orcamentos_abertos.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="55">
   <si>
     <t>Dt  Emissão</t>
   </si>
@@ -55,70 +55,127 @@
     <t>EYE PHARMA LTDA</t>
   </si>
   <si>
+    <t>BER SERVICOS DE ENGENHARIA E ARQ LTDA ME</t>
+  </si>
+  <si>
+    <t>DANILO</t>
+  </si>
+  <si>
+    <t>MONICA PATRICIA GUSMAO LIMA R DE CARVALHO</t>
+  </si>
+  <si>
+    <t>EDUARDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAR CONSTRUCOES E INCORPORACOES LTDA    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CELSO VIEIRA EMPREENDIMENTO IMOBILIARIO </t>
+  </si>
+  <si>
+    <t>PEDRO</t>
+  </si>
+  <si>
+    <t>RONALDO</t>
+  </si>
+  <si>
+    <t>LIVRARIA DA VILA LTDA</t>
+  </si>
+  <si>
+    <t>B2 BROOKLIN EMPREENDIMENTOS IMOBILIARIO SPE LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JB CONSTRUCOES E EMPREENDIMENTOS SCP ALESP </t>
+  </si>
+  <si>
+    <t xml:space="preserve">F REIS ENGENHARIA E CONSTRUCOES LTDA    </t>
+  </si>
+  <si>
+    <t>LUCA FABIANI</t>
+  </si>
+  <si>
+    <t>JHONE</t>
+  </si>
+  <si>
+    <t>DE BOER OBRAS DE ACABAMENTO LTDA</t>
+  </si>
+  <si>
+    <t>MIRANDA GUERRA EMPREEND E INCORP IMOB SPE LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REGO PAZOS ENG.CONSTRUCAO E COM.LTDA    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ORION ENGENHARIA E TECNOLOGIA S A       </t>
+  </si>
+  <si>
+    <t>PAULO DA SILVA ROSA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCOS CESAR P PORTO                    </t>
+  </si>
+  <si>
+    <t>ESTANPLAZA ADMINISTRADORA HOTELEIRA E COM LTDA SCP FUNCHAL</t>
+  </si>
+  <si>
+    <t>CONSTRUMIK COMERCIO E CONSTRUCAO LTDA</t>
+  </si>
+  <si>
+    <t>ALVES CONSTRUCOES E ENGENHARIA</t>
+  </si>
+  <si>
+    <t>M. EL HUSSEINI  CIA LTDA</t>
+  </si>
+  <si>
+    <t>OLECRAM EMPREENDIMENTOS E PARTIC LTDA ME</t>
+  </si>
+  <si>
+    <t>PRIME CONSTRUCOES LTDA</t>
+  </si>
+  <si>
     <t>MICHEL</t>
   </si>
   <si>
-    <t>SEMPRE ENGENHARIA E REPRESENTACOES LTDA</t>
-  </si>
-  <si>
-    <t>BER SERVICOS DE ENGENHARIA E ARQ LTDA ME</t>
-  </si>
-  <si>
-    <t>DANILO</t>
-  </si>
-  <si>
-    <t>MONICA PATRICIA GUSMAO LIMA R DE CARVALHO</t>
-  </si>
-  <si>
-    <t>EDUARDO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LAR CONSTRUCOES E INCORPORACOES LTDA    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">CELSO VIEIRA EMPREENDIMENTO IMOBILIARIO </t>
-  </si>
-  <si>
-    <t>PEDRO</t>
-  </si>
-  <si>
-    <t>RONALDO</t>
-  </si>
-  <si>
-    <t>LIVRARIA DA VILA LTDA</t>
-  </si>
-  <si>
-    <t>B2 BROOKLIN EMPREENDIMENTOS IMOBILIARIO SPE LTDA</t>
-  </si>
-  <si>
-    <t>IMBUIA CONSTRUTORA LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JB CONSTRUCOES E EMPREENDIMENTOS SCP ALESP </t>
-  </si>
-  <si>
-    <t xml:space="preserve">F REIS ENGENHARIA E CONSTRUCOES LTDA    </t>
+    <t>M BUILDING INCORP CONSTRUCAO LTDA</t>
+  </si>
+  <si>
+    <t>MTD PARTICIPACOES E SERVICOS TDA</t>
+  </si>
+  <si>
+    <t>DOROTI HISSAE MAEDA YAMAKAMI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMERCIAL E SERVICOS JVB S A            </t>
+  </si>
+  <si>
+    <t>LUIGGI CONTINI GER.DE PROJETOS OBRAS LTD</t>
+  </si>
+  <si>
+    <t>MR18 ENGENHARIA E CONSTRUCAO IMOVEIS LTD</t>
+  </si>
+  <si>
+    <t>KL ENGENHARIA EIRELI</t>
   </si>
   <si>
     <t>MACOR ENGENHARIA CONSTRUCOES E COMERC LT</t>
   </si>
   <si>
-    <t xml:space="preserve">SINNEN SISTEMAS INT DE ENGENHARIA LTDA  </t>
-  </si>
-  <si>
-    <t>LUCA FABIANI</t>
-  </si>
-  <si>
-    <t>JHONE</t>
-  </si>
-  <si>
-    <t>DE BOER OBRAS DE ACABAMENTO LTDA</t>
-  </si>
-  <si>
-    <t>MIRANDA GUERRA EMPREEND E INCORP IMOB SPE LTDA</t>
-  </si>
-  <si>
-    <t>141.535,98</t>
+    <t>MOBSTEEL EQUIPAMENTOS INOXIDAVEIS LTDA</t>
+  </si>
+  <si>
+    <t>COMERCIAL CONSTR E SERV BLANCHARD LTDA</t>
+  </si>
+  <si>
+    <t>CH3 CONSTRUTORA E INCORPORADORA LTDA</t>
+  </si>
+  <si>
+    <t>FRANCISCO GILSON CAVALCANTE MARINHO</t>
+  </si>
+  <si>
+    <t>MZI SPE 23 TIBIRICA LTDA</t>
+  </si>
+  <si>
+    <t>257.030,24</t>
   </si>
 </sst>
 </file>
@@ -522,7 +579,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F89"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22.28" customWidth="1"/>
@@ -655,19 +712,19 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <v>46139.38958333334</v>
+        <v>46139.39236111111</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C7" s="4">
-        <v>8384901</v>
+        <v>8385101</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E7" s="5">
-        <v>4154</v>
+        <v>46.06</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>8</v>
@@ -675,19 +732,19 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
-        <v>46139.39236111111</v>
+        <v>46139.410416666666</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C8" s="4">
-        <v>8385101</v>
+        <v>8385601</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E8" s="5">
-        <v>46.06</v>
+        <v>1278.19</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>8</v>
@@ -695,19 +752,19 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
-        <v>46139.410416666666</v>
+        <v>46139.41458333333</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C9" s="4">
-        <v>8385601</v>
+        <v>8385701</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E9" s="5">
-        <v>1278.19</v>
+        <v>2482.48</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>8</v>
@@ -715,19 +772,19 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
-        <v>46139.41458333333</v>
+        <v>46139.43888888889</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="4">
-        <v>8385701</v>
+        <v>8386601</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E10" s="5">
-        <v>2482.48</v>
+        <v>807.2</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>8</v>
@@ -735,19 +792,19 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
-        <v>46139.43888888889</v>
+        <v>46139.43958333333</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C11" s="4">
-        <v>8386601</v>
+        <v>8386701</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E11" s="5">
-        <v>807.2</v>
+        <v>2300.8</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>8</v>
@@ -755,19 +812,19 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
-        <v>46139.43958333333</v>
+        <v>46139.44930555555</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C12" s="4">
-        <v>8386701</v>
+        <v>8387201</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E12" s="5">
-        <v>2300.8</v>
+        <v>49.8</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>8</v>
@@ -775,19 +832,19 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
-        <v>46139.44930555555</v>
+        <v>46139.45138888889</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>17</v>
       </c>
       <c r="C13" s="4">
-        <v>8387201</v>
+        <v>8387301</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E13" s="5">
-        <v>49.8</v>
+        <v>14658.25</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>8</v>
@@ -795,19 +852,19 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
-        <v>46139.45138888889</v>
+        <v>46139.45972222222</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="4">
+        <v>8387401</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="4">
-        <v>8387301</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>20</v>
-      </c>
       <c r="E14" s="5">
-        <v>14538.32</v>
+        <v>770.38</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>8</v>
@@ -815,19 +872,19 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
-        <v>46139.45972222222</v>
+        <v>46139.46041666667</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="4">
-        <v>8387401</v>
+        <v>8387601</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="E15" s="5">
-        <v>770.38</v>
+        <v>179.5</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>8</v>
@@ -835,19 +892,19 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
-        <v>46139.46041666667</v>
+        <v>46139.4625</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="C16" s="4">
-        <v>8387601</v>
+        <v>8387701</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E16" s="5">
-        <v>179.5</v>
+        <v>612.92</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>8</v>
@@ -855,19 +912,19 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
-        <v>46139.4625</v>
+        <v>46139.46944444445</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C17" s="4">
-        <v>8387701</v>
+        <v>8388301</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E17" s="5">
-        <v>612.92</v>
+        <v>8436</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>8</v>
@@ -875,19 +932,19 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
-        <v>46139.46944444445</v>
+        <v>46139.47777777778</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C18" s="4">
-        <v>8388301</v>
+        <v>8388501</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E18" s="5">
-        <v>8436</v>
+        <v>2136.74</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>8</v>
@@ -895,19 +952,19 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
-        <v>46139.47777777778</v>
+        <v>46139.47986111111</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C19" s="4">
-        <v>8388501</v>
+        <v>8388601</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E19" s="5">
-        <v>2136.74</v>
+        <v>6718.86</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>8</v>
@@ -915,19 +972,19 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
-        <v>46139.47986111111</v>
+        <v>46139.49375</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C20" s="4">
-        <v>8388601</v>
+        <v>8389601</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E20" s="5">
-        <v>6718.86</v>
+        <v>532.85</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>8</v>
@@ -935,19 +992,19 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
-        <v>46139.49375</v>
+        <v>46139.49930555555</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C21" s="4">
-        <v>8389601</v>
+        <v>8389801</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E21" s="5">
-        <v>532.85</v>
+        <v>4472.17</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>8</v>
@@ -958,16 +1015,16 @@
         <v>46139.49930555555</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C22" s="4">
-        <v>8389801</v>
+        <v>8389901</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E22" s="5">
-        <v>4472.17</v>
+        <v>9705.84</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>8</v>
@@ -975,19 +1032,19 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
-        <v>46139.49930555555</v>
+        <v>46139.50347222222</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C23" s="4">
-        <v>8389901</v>
+        <v>8390101</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E23" s="5">
-        <v>9705.84</v>
+        <v>1539.57</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>8</v>
@@ -995,19 +1052,19 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
-        <v>46139.50347222222</v>
+        <v>46139.52013888889</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C24" s="4">
-        <v>8390101</v>
+        <v>8390701</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="E24" s="5">
-        <v>1539.57</v>
+        <v>2506.23</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>8</v>
@@ -1015,19 +1072,19 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
-        <v>46139.52013888889</v>
+        <v>46139.56388888889</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C25" s="4">
-        <v>8390701</v>
+        <v>8391501</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E25" s="5">
-        <v>2506.23</v>
+        <v>7928.1</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>8</v>
@@ -1035,19 +1092,19 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
-        <v>46139.56388888889</v>
+        <v>46139.57638888889</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C26" s="4">
-        <v>8391501</v>
+        <v>8391701</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E26" s="5">
-        <v>7928.1</v>
+        <v>2095</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>8</v>
@@ -1055,19 +1112,19 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
-        <v>46139.57638888889</v>
+        <v>46139.59861111111</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="C27" s="4">
-        <v>8391701</v>
+        <v>8392501</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E27" s="5">
-        <v>2095</v>
+        <v>4004.39</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>8</v>
@@ -1075,19 +1132,19 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
-        <v>46139.57986111111</v>
+        <v>46139.61944444444</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C28" s="4">
-        <v>8391901</v>
+        <v>8393201</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="E28" s="5">
-        <v>3637.67</v>
+        <v>6339.65</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>8</v>
@@ -1095,19 +1152,19 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
-        <v>46139.59236111111</v>
+        <v>46139.62291666667</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C29" s="4">
-        <v>8392301</v>
+        <v>8393401</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E29" s="5">
-        <v>4790.06</v>
+        <v>738.5</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>8</v>
@@ -1115,19 +1172,19 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
-        <v>46139.59861111111</v>
+        <v>46139.64166666666</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C30" s="4">
-        <v>8392501</v>
+        <v>8393801</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="E30" s="5">
-        <v>4004.39</v>
+        <v>5363.28</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>8</v>
@@ -1135,19 +1192,19 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
-        <v>46139.61944444444</v>
+        <v>46139.67222222222</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C31" s="4">
-        <v>8393201</v>
+        <v>8395001</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="E31" s="5">
-        <v>6339.65</v>
+        <v>3471.74</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>8</v>
@@ -1155,19 +1212,19 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
-        <v>46139.62291666667</v>
+        <v>46139.68194444444</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C32" s="4">
-        <v>8393401</v>
+        <v>8395101</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="E32" s="5">
-        <v>738.5</v>
+        <v>3604.02</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>8</v>
@@ -1175,19 +1232,19 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
-        <v>46139.64166666666</v>
+        <v>46139.68680555555</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="C33" s="4">
-        <v>8393801</v>
+        <v>8395301</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E33" s="5">
-        <v>5363.28</v>
+        <v>992.46</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>8</v>
@@ -1195,19 +1252,19 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
-        <v>46139.64791666667</v>
+        <v>46139.694444444445</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C34" s="4">
-        <v>8394201</v>
+        <v>8395701</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="E34" s="5">
-        <v>638.86</v>
+        <v>16322.38</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>8</v>
@@ -1215,19 +1272,19 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
-        <v>46139.65138888889</v>
+        <v>46139.70347222222</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="C35" s="4">
-        <v>8394501</v>
+        <v>8395901</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E35" s="5">
-        <v>2540.8</v>
+        <v>1567.75</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>8</v>
@@ -1235,19 +1292,19 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
-        <v>46139.67222222222</v>
+        <v>46139.72361111111</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C36" s="4">
-        <v>8395001</v>
+        <v>8396301</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E36" s="5">
-        <v>3471.74</v>
+        <v>571.2</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>8</v>
@@ -1255,19 +1312,19 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
-        <v>46139.68194444444</v>
+        <v>46139.74652777778</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C37" s="4">
-        <v>8395101</v>
+        <v>8396401</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E37" s="5">
-        <v>3604.02</v>
+        <v>1818.7</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>8</v>
@@ -1275,19 +1332,19 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
-        <v>46139.68680555555</v>
+        <v>46139.754166666666</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C38" s="4">
-        <v>8395301</v>
+        <v>8396601</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="E38" s="5">
-        <v>992.46</v>
+        <v>349.5</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>8</v>
@@ -1295,19 +1352,19 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
-        <v>46139.694444444445</v>
+        <v>46140.31736111111</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C39" s="4">
-        <v>8395701</v>
+        <v>8396701</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E39" s="5">
-        <v>16322.38</v>
+        <v>2035.45</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>8</v>
@@ -1315,19 +1372,19 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
-        <v>46139.70347222222</v>
+        <v>46140.325</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C40" s="4">
-        <v>8395901</v>
+        <v>8396801</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E40" s="5">
-        <v>1567.75</v>
+        <v>729.61</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>8</v>
@@ -1335,19 +1392,19 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
-        <v>46139.71388888889</v>
+        <v>46140.33125</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C41" s="4">
-        <v>8396001</v>
+        <v>8397001</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="E41" s="5">
-        <v>3692.06</v>
+        <v>566.06</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>8</v>
@@ -1355,19 +1412,19 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
-        <v>46139.72361111111</v>
+        <v>46140.3375</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="C42" s="4">
-        <v>8396301</v>
+        <v>8397101</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="E42" s="5">
-        <v>571.2</v>
+        <v>11312</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>8</v>
@@ -1375,19 +1432,19 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
-        <v>46139.74652777778</v>
+        <v>46140.34375</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C43" s="4">
-        <v>8396401</v>
+        <v>8397201</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E43" s="5">
-        <v>1818.7</v>
+        <v>549</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>8</v>
@@ -1395,31 +1452,911 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
-        <v>46139.754166666666</v>
+        <v>46140.35625</v>
       </c>
       <c r="B44" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C44" s="4">
+        <v>8397401</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E44" s="5">
+        <v>818</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="2">
+        <v>46140.37708333333</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="4">
+        <v>8397701</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E45" s="5">
+        <v>4454.63</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="2">
+        <v>46140.41111111111</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="4">
+        <v>8398701</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E46" s="5">
+        <v>1732.57</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="2">
+        <v>46140.413194444445</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C47" s="4">
+        <v>8398801</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E47" s="5">
+        <v>3394.98</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="2">
+        <v>46140.413888888885</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C48" s="4">
+        <v>8398901</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E48" s="5">
+        <v>1783.65</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="2">
+        <v>46140.42083333334</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C49" s="4">
+        <v>8399101</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E49" s="5">
+        <v>754.5</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="2">
+        <v>46140.42638888889</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C50" s="4">
+        <v>8399401</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E50" s="5">
+        <v>2223</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="2">
+        <v>46140.43263888889</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C51" s="4">
+        <v>8399501</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E51" s="5">
+        <v>3095.38</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="2">
+        <v>46140.44027777778</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="4">
+        <v>8399801</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E52" s="5">
+        <v>1217.07</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="2">
+        <v>46140.44375</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C53" s="4">
+        <v>8399901</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E53" s="5">
+        <v>1474.89</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="2">
+        <v>46140.444444444445</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C54" s="4">
+        <v>8400001</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E54" s="5">
+        <v>471.4</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="2">
+        <v>46140.447222222225</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C55" s="4">
+        <v>8400101</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E55" s="5">
+        <v>2041.6</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="2">
+        <v>46140.44930555555</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C56" s="4">
+        <v>8400301</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E56" s="5">
+        <v>1221.75</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="2">
+        <v>46140.45694444445</v>
+      </c>
+      <c r="B57" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C44" s="4">
-        <v>8396601</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E44" s="5">
-        <v>349.5</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E45" s="6" t="s">
-        <v>35</v>
+      <c r="C57" s="4">
+        <v>8400501</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E57" s="5">
+        <v>3502.27</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="2">
+        <v>46140.461805555555</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C58" s="4">
+        <v>8400901</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E58" s="5">
+        <v>5473.8</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="2">
+        <v>46140.47152777778</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C59" s="4">
+        <v>8401001</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E59" s="5">
+        <v>3317.4</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="2">
+        <v>46140.472916666666</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C60" s="4">
+        <v>8401101</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E60" s="5">
+        <v>4070.7</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="2">
+        <v>46140.47708333333</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C61" s="4">
+        <v>8401201</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E61" s="5">
+        <v>2803.91</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="2">
+        <v>46140.48402777778</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C62" s="4">
+        <v>8401501</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E62" s="5">
+        <v>225</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="2">
+        <v>46140.50138888889</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C63" s="4">
+        <v>8402401</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E63" s="5">
+        <v>773.45</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="2">
+        <v>46140.50833333333</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C64" s="4">
+        <v>8402601</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E64" s="5">
+        <v>16080.43</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="2">
+        <v>46140.52291666667</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C65" s="4">
+        <v>8403101</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E65" s="5">
+        <v>1887.54</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="2">
+        <v>46140.52777777778</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C66" s="4">
+        <v>8403301</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E66" s="5">
+        <v>2706.34</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="2">
+        <v>46140.56458333333</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C67" s="4">
+        <v>8403801</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E67" s="5">
+        <v>2719.24</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="2">
+        <v>46140.58125</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C68" s="4">
+        <v>8404301</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E68" s="5">
+        <v>6856</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="2">
+        <v>46140.586111111115</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C69" s="4">
+        <v>8404601</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E69" s="5">
+        <v>1278.88</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="2">
+        <v>46140.59930555556</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C70" s="4">
+        <v>8404901</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E70" s="5">
+        <v>1137.3</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="2">
+        <v>46140.60486111111</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C71" s="4">
+        <v>8405201</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E71" s="5">
+        <v>958.34</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="2">
+        <v>46140.62569444445</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C72" s="4">
+        <v>8405601</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E72" s="5">
+        <v>9954</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" s="2">
+        <v>46140.62708333333</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C73" s="4">
+        <v>8405701</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E73" s="5">
+        <v>619</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" s="2">
+        <v>46140.63541666667</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C74" s="4">
+        <v>8406001</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E74" s="5">
+        <v>969.69</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="2">
+        <v>46140.63541666667</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C75" s="4">
+        <v>8406101</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E75" s="5">
+        <v>3342.08</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" s="2">
+        <v>46140.63680555555</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C76" s="4">
+        <v>8406301</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E76" s="5">
+        <v>3827.37</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" s="2">
+        <v>46140.64444444445</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C77" s="4">
+        <v>8406601</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E77" s="5">
+        <v>5146.13</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="2">
+        <v>46140.65277777778</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C78" s="4">
+        <v>8406901</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E78" s="5">
+        <v>751.53</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" s="2">
+        <v>46140.66111111111</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C79" s="4">
+        <v>8407401</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E79" s="5">
+        <v>199.7</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" s="2">
+        <v>46140.6625</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C80" s="4">
+        <v>8407501</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E80" s="5">
+        <v>1726</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" s="2">
+        <v>46140.68541666667</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C81" s="4">
+        <v>8408001</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E81" s="5">
+        <v>1047</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" s="2">
+        <v>46140.68611111111</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C82" s="4">
+        <v>8408201</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E82" s="5">
+        <v>206.7</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" s="2">
+        <v>46140.69652777778</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C83" s="4">
+        <v>8408401</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E83" s="5">
+        <v>1462.78</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" s="2">
+        <v>46140.700694444444</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C84" s="4">
+        <v>8408701</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E84" s="5">
+        <v>3537.57</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" s="2">
+        <v>46140.70347222222</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C85" s="4">
+        <v>8408801</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E85" s="5">
+        <v>1229.4</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" s="2">
+        <v>46140.70763888889</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C86" s="4">
+        <v>8408901</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E86" s="5">
+        <v>1742.7</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" s="2">
+        <v>46140.711111111115</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C87" s="4">
+        <v>8409101</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E87" s="5">
+        <v>1130.48</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" s="2">
+        <v>46140.7375</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C88" s="4">
+        <v>8409401</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E88" s="5">
+        <v>4269.51</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E89" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F45"/>
+  <autoFilter ref="A1:F89"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
